--- a/article-review-main.xlsx
+++ b/article-review-main.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/_studium/2-Kurse/04 - DLMAISAIS - AI and Society/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/_studium/2-Kurse/04 - DLMAISAIS - AI and Society/DLMAISAIS-references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AE32A4-A856-4D4F-AB64-FC5E182D4D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D230E137-E64A-704A-B93E-97F200F6654D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{3049AA78-95CF-1142-9BB5-B669FE93D892}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="main" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$Q$100</definedName>
-    <definedName name="articles" localSheetId="0">main!$A$1:$Q$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$100</definedName>
+    <definedName name="articles" localSheetId="0">main!$A$1:$R$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="758">
   <si>
     <t>key</t>
   </si>
@@ -2301,6 +2301,51 @@
   </si>
   <si>
     <t>Supply Chain &amp; Ops; Sustainability</t>
+  </si>
+  <si>
+    <t>citeReference</t>
+  </si>
+  <si>
+    <t>yakovenko_transformative_2022</t>
+  </si>
+  <si>
+    <t>rukadikar_adoption_2023</t>
+  </si>
+  <si>
+    <t>hemalatha_impact_2021</t>
+  </si>
+  <si>
+    <t>ranjan_das_artificial_2023</t>
+  </si>
+  <si>
+    <t>kumar_tyagi_impact_2023</t>
+  </si>
+  <si>
+    <t>manoharan_future_2024</t>
+  </si>
+  <si>
+    <t>samman_ai-driven_2024</t>
+  </si>
+  <si>
+    <t>madhavi_impact_2024</t>
+  </si>
+  <si>
+    <t>wang_ai_2023</t>
+  </si>
+  <si>
+    <t>singh_impact_2021</t>
+  </si>
+  <si>
+    <t>liu_embracing_2024</t>
+  </si>
+  <si>
+    <t>aditya_significance_2023</t>
+  </si>
+  <si>
+    <t>sharma_ai_2024</t>
+  </si>
+  <si>
+    <t>la_torre_team_2023</t>
   </si>
 </sst>
 </file>
@@ -2339,7 +2384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2376,6 +2421,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2390,7 +2441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2401,6 +2452,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2747,13 +2802,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A20306-08DA-394C-A3B0-22BFD9DFB649}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:R131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="2" width="7.5" customWidth="1"/>
-    <col min="3" max="3" width="5.5" customWidth="1"/>
-    <col min="4" max="4" width="93.83203125" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" customWidth="1"/>
+    <col min="4" max="4" width="99.5" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="14.1640625" customWidth="1"/>
     <col min="7" max="7" width="11.83203125" customWidth="1"/>
@@ -2763,13 +2818,13 @@
     <col min="11" max="11" width="46.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.83203125" customWidth="1"/>
     <col min="13" max="13" width="46.6640625" style="8" customWidth="1"/>
-    <col min="14" max="14" width="31" customWidth="1"/>
-    <col min="15" max="15" width="84.83203125" customWidth="1"/>
-    <col min="16" max="16" width="44.6640625" customWidth="1"/>
-    <col min="17" max="17" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="31" customWidth="1"/>
+    <col min="16" max="16" width="84.83203125" customWidth="1"/>
+    <col min="17" max="17" width="44.6640625" customWidth="1"/>
+    <col min="18" max="18" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2812,17 +2867,20 @@
       <c r="N1" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="P1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>575</v>
       </c>
@@ -2865,17 +2923,17 @@
       <c r="N2" t="s">
         <v>682</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>11</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>576</v>
       </c>
@@ -2919,17 +2977,17 @@
       <c r="N3" t="s">
         <v>686</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>16</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>577</v>
       </c>
@@ -2973,18 +3031,18 @@
       <c r="N4" t="s">
         <v>687</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>21</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>578</v>
       </c>
       <c r="B5">
@@ -3017,17 +3075,18 @@
       <c r="L5" s="4"/>
       <c r="M5" s="1"/>
       <c r="N5" s="4"/>
-      <c r="O5" t="s">
+      <c r="O5" s="4"/>
+      <c r="P5" t="s">
         <v>26</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>25</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>579</v>
       </c>
@@ -3070,18 +3129,18 @@
       <c r="N6" t="s">
         <v>682</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>31</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>580</v>
       </c>
       <c r="B7">
@@ -3114,28 +3173,29 @@
       <c r="L7" s="4"/>
       <c r="M7" s="1"/>
       <c r="N7" s="4"/>
-      <c r="O7" t="s">
+      <c r="O7" s="4"/>
+      <c r="P7" t="s">
         <v>36</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B8">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>498</v>
@@ -3143,7 +3203,7 @@
       <c r="F8" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>498</v>
       </c>
       <c r="H8" t="s">
@@ -3153,31 +3213,34 @@
         <v>680</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="L8" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="M8" t="s">
         <v>688</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O8" t="s">
-        <v>41</v>
+      <c r="O8" s="13" t="s">
+        <v>755</v>
       </c>
       <c r="P8" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="Q8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="R8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>582</v>
       </c>
@@ -3197,7 +3260,7 @@
         <v>498</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E9=F9, E9, "-")</f>
         <v>Included</v>
       </c>
       <c r="H9" t="s">
@@ -3221,17 +3284,17 @@
       <c r="N9" t="s">
         <v>689</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>46</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>45</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>583</v>
       </c>
@@ -3251,7 +3314,7 @@
         <v>498</v>
       </c>
       <c r="G10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E10=F10, E10, "-")</f>
         <v>Included</v>
       </c>
       <c r="H10" t="s">
@@ -3275,17 +3338,17 @@
       <c r="N10" t="s">
         <v>687</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>51</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>50</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>584</v>
       </c>
@@ -3305,7 +3368,7 @@
         <v>498</v>
       </c>
       <c r="G11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E11=F11, E11, "-")</f>
         <v>Included</v>
       </c>
       <c r="H11" t="s">
@@ -3329,17 +3392,17 @@
       <c r="N11" t="s">
         <v>690</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>56</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>55</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>585</v>
       </c>
@@ -3359,7 +3422,7 @@
         <v>498</v>
       </c>
       <c r="G12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E12=F12, E12, "-")</f>
         <v>Included</v>
       </c>
       <c r="H12" t="s">
@@ -3383,18 +3446,18 @@
       <c r="N12" t="s">
         <v>682</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>61</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>60</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>586</v>
       </c>
       <c r="B13">
@@ -3413,7 +3476,7 @@
         <v>500</v>
       </c>
       <c r="G13" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E13=F13, E13, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H13" t="s">
@@ -3428,71 +3491,76 @@
       <c r="L13" s="4"/>
       <c r="M13" s="1"/>
       <c r="N13" s="4"/>
-      <c r="O13" t="s">
+      <c r="O13" s="4"/>
+      <c r="P13" t="s">
         <v>66</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="B14">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
         <v>498</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>498</v>
+      <c r="F14" t="s">
+        <v>498</v>
+      </c>
+      <c r="G14" s="2" t="str">
+        <f>IF(E14=F14, E14, "-")</f>
+        <v>Included</v>
       </c>
       <c r="H14" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I14" t="s">
         <v>680</v>
       </c>
       <c r="J14" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="L14" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="M14" t="s">
+        <v>729</v>
+      </c>
+      <c r="N14" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="N14" t="s">
-        <v>688</v>
-      </c>
-      <c r="O14" t="s">
-        <v>71</v>
+      <c r="O14" s="13" t="s">
+        <v>744</v>
       </c>
       <c r="P14" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="Q14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="R14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
         <v>588</v>
       </c>
       <c r="B15">
@@ -3525,18 +3593,19 @@
       <c r="L15" s="4"/>
       <c r="M15" s="1"/>
       <c r="N15" s="4"/>
-      <c r="O15" t="s">
+      <c r="O15" s="4"/>
+      <c r="P15" t="s">
         <v>76</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>75</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>589</v>
       </c>
       <c r="B16">
@@ -3569,17 +3638,18 @@
       <c r="L16" s="4"/>
       <c r="M16" s="1"/>
       <c r="N16" s="4"/>
-      <c r="O16" t="s">
+      <c r="O16" s="4"/>
+      <c r="P16" t="s">
         <v>81</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>80</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>590</v>
       </c>
@@ -3599,7 +3669,7 @@
         <v>498</v>
       </c>
       <c r="G17" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E17=F17, E17, "-")</f>
         <v>Included</v>
       </c>
       <c r="H17" t="s">
@@ -3623,17 +3693,17 @@
       <c r="N17" t="s">
         <v>689</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>86</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>85</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>591</v>
       </c>
@@ -3676,17 +3746,17 @@
       <c r="N18" t="s">
         <v>685</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>91</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>90</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>592</v>
       </c>
@@ -3706,7 +3776,7 @@
         <v>498</v>
       </c>
       <c r="G19" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E19=F19, E19, "-")</f>
         <v>Included</v>
       </c>
       <c r="H19" t="s">
@@ -3730,17 +3800,17 @@
       <c r="N19" t="s">
         <v>685</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>96</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>95</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>593</v>
       </c>
@@ -3760,7 +3830,7 @@
         <v>498</v>
       </c>
       <c r="G20" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E20=F20, E20, "-")</f>
         <v>Included</v>
       </c>
       <c r="H20" t="s">
@@ -3784,17 +3854,17 @@
       <c r="N20" t="s">
         <v>691</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>101</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>100</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>594</v>
       </c>
@@ -3814,7 +3884,7 @@
         <v>498</v>
       </c>
       <c r="G21" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E21=F21, E21, "-")</f>
         <v>Included</v>
       </c>
       <c r="H21" t="s">
@@ -3838,17 +3908,17 @@
       <c r="N21" t="s">
         <v>686</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>106</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>105</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>595</v>
       </c>
@@ -3891,17 +3961,17 @@
       <c r="N22" t="s">
         <v>690</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>111</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>110</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>596</v>
       </c>
@@ -3944,17 +4014,17 @@
       <c r="N23" t="s">
         <v>683</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>116</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>115</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>597</v>
       </c>
@@ -3974,7 +4044,7 @@
         <v>498</v>
       </c>
       <c r="G24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E24=F24, E24, "-")</f>
         <v>Included</v>
       </c>
       <c r="H24" t="s">
@@ -3998,18 +4068,18 @@
       <c r="N24" t="s">
         <v>683</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>121</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>120</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>598</v>
       </c>
       <c r="B25">
@@ -4042,17 +4112,18 @@
       <c r="L25" s="4"/>
       <c r="M25" s="1"/>
       <c r="N25" s="4"/>
-      <c r="O25" t="s">
+      <c r="O25" s="4"/>
+      <c r="P25" t="s">
         <v>126</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>125</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>599</v>
       </c>
@@ -4095,71 +4166,73 @@
       <c r="N26" t="s">
         <v>685</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>131</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>130</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="B27">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="E27" t="s">
         <v>498</v>
       </c>
       <c r="F27" t="s">
-        <v>498</v>
-      </c>
-      <c r="G27" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Included</v>
+        <v>500</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>498</v>
       </c>
       <c r="H27" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="I27" t="s">
         <v>680</v>
       </c>
       <c r="J27" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="L27" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="M27" t="s">
         <v>729</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N27" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O27" t="s">
-        <v>136</v>
+      <c r="O27" s="13" t="s">
+        <v>745</v>
       </c>
       <c r="P27" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="Q27" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+      <c r="R27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>601</v>
       </c>
@@ -4202,17 +4275,17 @@
       <c r="N28" t="s">
         <v>685</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>141</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>140</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>602</v>
       </c>
@@ -4232,7 +4305,7 @@
         <v>498</v>
       </c>
       <c r="G29" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E29=F29, E29, "-")</f>
         <v>Included</v>
       </c>
       <c r="H29" t="s">
@@ -4256,18 +4329,18 @@
       <c r="N29" t="s">
         <v>682</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>146</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>145</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>603</v>
       </c>
       <c r="B30">
@@ -4286,7 +4359,7 @@
         <v>500</v>
       </c>
       <c r="G30" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E30=F30, E30, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H30" t="s">
@@ -4301,18 +4374,19 @@
       <c r="L30" s="4"/>
       <c r="M30" s="1"/>
       <c r="N30" s="4"/>
-      <c r="O30" t="s">
+      <c r="O30" s="4"/>
+      <c r="P30" t="s">
         <v>151</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>150</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
         <v>604</v>
       </c>
       <c r="B31">
@@ -4345,17 +4419,18 @@
       <c r="L31" s="4"/>
       <c r="M31" s="1"/>
       <c r="N31" s="4"/>
-      <c r="O31" t="s">
+      <c r="O31" s="4"/>
+      <c r="P31" t="s">
         <v>156</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>155</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>605</v>
       </c>
@@ -4398,17 +4473,17 @@
       <c r="N32" t="s">
         <v>685</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>161</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>160</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>606</v>
       </c>
@@ -4428,7 +4503,7 @@
         <v>498</v>
       </c>
       <c r="G33" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E33=F33, E33, "-")</f>
         <v>Included</v>
       </c>
       <c r="H33" t="s">
@@ -4452,17 +4527,17 @@
       <c r="N33" t="s">
         <v>686</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>166</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>165</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>607</v>
       </c>
@@ -4482,7 +4557,7 @@
         <v>498</v>
       </c>
       <c r="G34" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E34=F34, E34, "-")</f>
         <v>Included</v>
       </c>
       <c r="H34" t="s">
@@ -4506,18 +4581,18 @@
       <c r="N34" t="s">
         <v>685</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>170</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>169</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="10" t="s">
         <v>608</v>
       </c>
       <c r="B35">
@@ -4536,7 +4611,7 @@
         <v>500</v>
       </c>
       <c r="G35" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E35=F35, E35, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H35" t="s">
@@ -4551,18 +4626,19 @@
       <c r="L35" s="4"/>
       <c r="M35" s="1"/>
       <c r="N35" s="4"/>
-      <c r="O35" t="s">
+      <c r="O35" s="4"/>
+      <c r="P35" t="s">
         <v>175</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>174</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="s">
         <v>609</v>
       </c>
       <c r="B36">
@@ -4595,17 +4671,18 @@
       <c r="L36" s="4"/>
       <c r="M36" s="1"/>
       <c r="N36" s="4"/>
-      <c r="O36" t="s">
+      <c r="O36" s="4"/>
+      <c r="P36" t="s">
         <v>179</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>178</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>610</v>
       </c>
@@ -4622,7 +4699,7 @@
         <v>498</v>
       </c>
       <c r="G37" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E37=F37, E37, "-")</f>
         <v>Included</v>
       </c>
       <c r="H37" t="s">
@@ -4646,70 +4723,73 @@
       <c r="N37" t="s">
         <v>689</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>184</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>183</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B38">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E38" t="s">
         <v>498</v>
       </c>
-      <c r="F38" t="s">
-        <v>500</v>
-      </c>
-      <c r="G38" s="3" t="s">
+      <c r="F38" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>498</v>
       </c>
       <c r="H38" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="I38" t="s">
         <v>680</v>
       </c>
       <c r="J38" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L38" t="s">
         <v>698</v>
       </c>
       <c r="M38" t="s">
-        <v>729</v>
-      </c>
-      <c r="N38" t="s">
         <v>688</v>
       </c>
-      <c r="O38" t="s">
-        <v>189</v>
+      <c r="N38" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>756</v>
       </c>
       <c r="P38" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="Q38" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+      <c r="R38" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>612</v>
       </c>
@@ -4752,49 +4832,50 @@
       <c r="N39" t="s">
         <v>683</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>194</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>193</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B40">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="E40" t="s">
         <v>498</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>498</v>
+      <c r="F40" t="s">
+        <v>498</v>
+      </c>
+      <c r="G40" s="2" t="str">
+        <f>IF(E40=F40, E40, "-")</f>
+        <v>Included</v>
       </c>
       <c r="H40" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I40" t="s">
         <v>680</v>
       </c>
       <c r="J40" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L40" t="s">
         <v>698</v>
@@ -4802,21 +4883,24 @@
       <c r="M40" t="s">
         <v>688</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O40" t="s">
-        <v>199</v>
+      <c r="O40" s="13" t="s">
+        <v>746</v>
       </c>
       <c r="P40" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="Q40" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+        <v>212</v>
+      </c>
+      <c r="R40" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="10" t="s">
         <v>614</v>
       </c>
       <c r="B41">
@@ -4843,14 +4927,15 @@
       <c r="L41" s="4"/>
       <c r="M41" s="1"/>
       <c r="N41" s="4"/>
-      <c r="O41" t="s">
+      <c r="O41" s="4"/>
+      <c r="P41" t="s">
         <v>205</v>
       </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>615</v>
       </c>
@@ -4870,7 +4955,7 @@
         <v>498</v>
       </c>
       <c r="G42" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E42=F42, E42, "-")</f>
         <v>Included</v>
       </c>
       <c r="H42" t="s">
@@ -4894,28 +4979,28 @@
       <c r="N42" t="s">
         <v>682</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>208</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>207</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="B43">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="E43" t="s">
         <v>498</v>
@@ -4924,7 +5009,7 @@
         <v>498</v>
       </c>
       <c r="G43" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E43=F43, E43, "-")</f>
         <v>Included</v>
       </c>
       <c r="H43" t="s">
@@ -4934,32 +5019,35 @@
         <v>680</v>
       </c>
       <c r="J43" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="L43" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="M43" t="s">
+        <v>729</v>
+      </c>
+      <c r="N43" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="N43" t="s">
-        <v>688</v>
-      </c>
-      <c r="O43" t="s">
-        <v>213</v>
+      <c r="O43" s="13" t="s">
+        <v>757</v>
       </c>
       <c r="P43" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="Q43" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+        <v>247</v>
+      </c>
+      <c r="R43" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="10" t="s">
         <v>617</v>
       </c>
       <c r="B44">
@@ -4992,18 +5080,19 @@
       <c r="L44" s="4"/>
       <c r="M44" s="1"/>
       <c r="N44" s="4"/>
-      <c r="O44" t="s">
+      <c r="O44" s="4"/>
+      <c r="P44" t="s">
         <v>218</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>217</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="10" t="s">
         <v>618</v>
       </c>
       <c r="B45">
@@ -5036,17 +5125,18 @@
       <c r="L45" s="4"/>
       <c r="M45" s="1"/>
       <c r="N45" s="4"/>
-      <c r="O45" t="s">
+      <c r="O45" s="4"/>
+      <c r="P45" t="s">
         <v>223</v>
       </c>
-      <c r="P45" t="s">
+      <c r="Q45" t="s">
         <v>222</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>619</v>
       </c>
@@ -5089,17 +5179,17 @@
       <c r="N46" t="s">
         <v>682</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P46" t="s">
         <v>228</v>
       </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
         <v>227</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="R46" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>620</v>
       </c>
@@ -5142,17 +5232,17 @@
       <c r="N47" t="s">
         <v>685</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>233</v>
       </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>232</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>621</v>
       </c>
@@ -5172,7 +5262,7 @@
         <v>498</v>
       </c>
       <c r="G48" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E48=F48, E48, "-")</f>
         <v>Included</v>
       </c>
       <c r="H48" t="s">
@@ -5196,18 +5286,18 @@
       <c r="N48" t="s">
         <v>687</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>238</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>237</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="10" t="s">
         <v>622</v>
       </c>
       <c r="B49">
@@ -5237,72 +5327,75 @@
       <c r="L49" s="4"/>
       <c r="M49" s="1"/>
       <c r="N49" s="4"/>
-      <c r="O49" t="s">
+      <c r="O49" s="4"/>
+      <c r="P49" t="s">
         <v>243</v>
       </c>
-      <c r="P49" t="s">
+      <c r="Q49" t="s">
         <v>242</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B50">
         <v>2023</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="E50" t="s">
         <v>498</v>
       </c>
-      <c r="F50" t="s">
-        <v>498</v>
-      </c>
-      <c r="G50" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Included</v>
+      <c r="F50" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>498</v>
       </c>
       <c r="H50" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I50" t="s">
         <v>680</v>
       </c>
       <c r="J50" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="L50" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="M50" t="s">
-        <v>729</v>
-      </c>
-      <c r="N50" t="s">
         <v>688</v>
       </c>
-      <c r="O50" t="s">
-        <v>248</v>
+      <c r="N50" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="O50" s="13" t="s">
+        <v>747</v>
       </c>
       <c r="P50" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="Q50" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+        <v>272</v>
+      </c>
+      <c r="R50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="10" t="s">
         <v>624</v>
       </c>
       <c r="B51">
@@ -5335,17 +5428,18 @@
       <c r="L51" s="4"/>
       <c r="M51" s="1"/>
       <c r="N51" s="4"/>
-      <c r="O51" t="s">
+      <c r="O51" s="4"/>
+      <c r="P51" t="s">
         <v>253</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>252</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
         <v>625</v>
       </c>
@@ -5388,17 +5482,17 @@
       <c r="N52" t="s">
         <v>685</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
         <v>258</v>
       </c>
-      <c r="P52" t="s">
+      <c r="Q52" t="s">
         <v>257</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="R52" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>626</v>
       </c>
@@ -5441,17 +5535,17 @@
       <c r="N53" t="s">
         <v>685</v>
       </c>
-      <c r="O53" t="s">
+      <c r="P53" t="s">
         <v>263</v>
       </c>
-      <c r="P53" t="s">
+      <c r="Q53" t="s">
         <v>262</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="R53" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
         <v>627</v>
       </c>
@@ -5494,19 +5588,19 @@
       <c r="N54" t="s">
         <v>685</v>
       </c>
-      <c r="O54" t="s">
+      <c r="P54" t="s">
         <v>268</v>
       </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
         <v>267</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B55">
         <v>2023</v>
@@ -5515,7 +5609,7 @@
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="E55" t="s">
         <v>498</v>
@@ -5533,10 +5627,10 @@
         <v>680</v>
       </c>
       <c r="J55" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L55" t="s">
         <v>698</v>
@@ -5544,20 +5638,23 @@
       <c r="M55" t="s">
         <v>688</v>
       </c>
-      <c r="N55" t="s">
+      <c r="N55" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O55" t="s">
-        <v>273</v>
+      <c r="O55" s="13" t="s">
+        <v>748</v>
       </c>
       <c r="P55" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="Q55" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+      <c r="R55" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
         <v>629</v>
       </c>
@@ -5577,7 +5674,7 @@
         <v>498</v>
       </c>
       <c r="G56" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E56=F56, E56, "-")</f>
         <v>Included</v>
       </c>
       <c r="H56" t="s">
@@ -5601,28 +5698,28 @@
       <c r="N56" t="s">
         <v>686</v>
       </c>
-      <c r="O56" t="s">
+      <c r="P56" t="s">
         <v>278</v>
       </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
         <v>277</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="R56" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="B57">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C57">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="E57" t="s">
         <v>498</v>
@@ -5640,32 +5737,35 @@
         <v>680</v>
       </c>
       <c r="J57" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="L57" t="s">
         <v>698</v>
       </c>
       <c r="M57" t="s">
+        <v>729</v>
+      </c>
+      <c r="N57" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="N57" t="s">
-        <v>688</v>
-      </c>
-      <c r="O57" t="s">
-        <v>283</v>
+      <c r="O57" s="13" t="s">
+        <v>749</v>
       </c>
       <c r="P57" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="Q57" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+        <v>341</v>
+      </c>
+      <c r="R57" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="10" t="s">
         <v>631</v>
       </c>
       <c r="B58">
@@ -5692,14 +5792,15 @@
       <c r="L58" s="4"/>
       <c r="M58" s="1"/>
       <c r="N58" s="4"/>
-      <c r="O58" t="s">
+      <c r="O58" s="4"/>
+      <c r="P58" t="s">
         <v>289</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
         <v>632</v>
       </c>
@@ -5742,18 +5843,18 @@
       <c r="N59" t="s">
         <v>692</v>
       </c>
-      <c r="O59" t="s">
+      <c r="P59" t="s">
         <v>292</v>
       </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>291</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="R59" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="10" t="s">
         <v>633</v>
       </c>
       <c r="B60">
@@ -5786,18 +5887,19 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
-      <c r="O60" t="s">
+      <c r="O60" s="4"/>
+      <c r="P60" t="s">
         <v>297</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>296</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="R60" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="10" t="s">
         <v>634</v>
       </c>
       <c r="B61">
@@ -5830,18 +5932,19 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
-      <c r="O61" t="s">
+      <c r="O61" s="4"/>
+      <c r="P61" t="s">
         <v>302</v>
       </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
         <v>301</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="R61" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="10" t="s">
         <v>635</v>
       </c>
       <c r="B62">
@@ -5874,18 +5977,19 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
-      <c r="O62" t="s">
+      <c r="O62" s="4"/>
+      <c r="P62" t="s">
         <v>307</v>
       </c>
-      <c r="P62" t="s">
+      <c r="Q62" t="s">
         <v>306</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="10" t="s">
         <v>636</v>
       </c>
       <c r="B63">
@@ -5904,7 +6008,7 @@
         <v>500</v>
       </c>
       <c r="G63" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E63=F63, E63, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H63" t="s">
@@ -5919,17 +6023,18 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
-      <c r="O63" t="s">
+      <c r="O63" s="4"/>
+      <c r="P63" t="s">
         <v>312</v>
       </c>
-      <c r="P63" t="s">
+      <c r="Q63" t="s">
         <v>311</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="R63" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
         <v>637</v>
       </c>
@@ -5972,17 +6077,17 @@
       <c r="N64" t="s">
         <v>683</v>
       </c>
-      <c r="O64" t="s">
+      <c r="P64" t="s">
         <v>317</v>
       </c>
-      <c r="P64" t="s">
+      <c r="Q64" t="s">
         <v>316</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="R64" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="s">
         <v>638</v>
       </c>
@@ -6025,17 +6130,17 @@
       <c r="N65" t="s">
         <v>685</v>
       </c>
-      <c r="O65" t="s">
+      <c r="P65" t="s">
         <v>322</v>
       </c>
-      <c r="P65" t="s">
+      <c r="Q65" t="s">
         <v>321</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R65" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
         <v>639</v>
       </c>
@@ -6078,18 +6183,18 @@
       <c r="N66" t="s">
         <v>690</v>
       </c>
-      <c r="O66" t="s">
+      <c r="P66" t="s">
         <v>327</v>
       </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
         <v>326</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="10" t="s">
         <v>640</v>
       </c>
       <c r="B67">
@@ -6108,7 +6213,7 @@
         <v>500</v>
       </c>
       <c r="G67" s="2" t="str">
-        <f t="shared" ref="G67:G83" si="1">IF(E67=F67, E67, "-")</f>
+        <f>IF(E67=F67, E67, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H67" t="s">
@@ -6123,17 +6228,18 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
-      <c r="O67" t="s">
+      <c r="O67" s="4"/>
+      <c r="P67" t="s">
         <v>332</v>
       </c>
-      <c r="P67" t="s">
+      <c r="Q67" t="s">
         <v>331</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="R67" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="s">
         <v>641</v>
       </c>
@@ -6153,7 +6259,7 @@
         <v>498</v>
       </c>
       <c r="G68" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E68=F68, E68, "-")</f>
         <v>Included</v>
       </c>
       <c r="H68" t="s">
@@ -6177,28 +6283,28 @@
       <c r="N68" t="s">
         <v>685</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P68" t="s">
         <v>337</v>
       </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>336</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="9" t="s">
-        <v>642</v>
+        <v>581</v>
       </c>
       <c r="B69">
         <v>2024</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="E69" t="s">
         <v>498</v>
@@ -6206,7 +6312,7 @@
       <c r="F69" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G69" s="5" t="s">
         <v>498</v>
       </c>
       <c r="H69" t="s">
@@ -6216,32 +6322,35 @@
         <v>680</v>
       </c>
       <c r="J69" t="s">
-        <v>343</v>
+        <v>42</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="L69" t="s">
         <v>698</v>
       </c>
       <c r="M69" t="s">
-        <v>729</v>
-      </c>
-      <c r="N69" t="s">
         <v>688</v>
       </c>
-      <c r="O69" t="s">
-        <v>342</v>
+      <c r="N69" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="O69" s="13" t="s">
+        <v>751</v>
       </c>
       <c r="P69" t="s">
-        <v>341</v>
+        <v>41</v>
       </c>
       <c r="Q69" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+        <v>40</v>
+      </c>
+      <c r="R69" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="10" t="s">
         <v>643</v>
       </c>
       <c r="B70">
@@ -6271,17 +6380,18 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
-      <c r="O70" t="s">
+      <c r="O70" s="4"/>
+      <c r="P70" t="s">
         <v>347</v>
       </c>
-      <c r="P70" t="s">
+      <c r="Q70" t="s">
         <v>346</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="s">
         <v>644</v>
       </c>
@@ -6324,17 +6434,17 @@
       <c r="N71" t="s">
         <v>685</v>
       </c>
-      <c r="O71" t="s">
+      <c r="P71" t="s">
         <v>352</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>351</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
         <v>645</v>
       </c>
@@ -6354,7 +6464,7 @@
         <v>498</v>
       </c>
       <c r="G72" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E72=F72, E72, "-")</f>
         <v>Included</v>
       </c>
       <c r="H72" t="s">
@@ -6375,21 +6485,24 @@
       <c r="M72" t="s">
         <v>741</v>
       </c>
-      <c r="N72" t="s">
+      <c r="N72" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O72" t="s">
+      <c r="O72" s="13" t="s">
+        <v>750</v>
+      </c>
+      <c r="P72" t="s">
         <v>357</v>
       </c>
-      <c r="P72" t="s">
+      <c r="Q72" t="s">
         <v>356</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="R72" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="s">
         <v>646</v>
       </c>
       <c r="B73">
@@ -6422,18 +6535,19 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
-      <c r="O73" t="s">
+      <c r="O73" s="4"/>
+      <c r="P73" t="s">
         <v>362</v>
       </c>
-      <c r="P73" t="s">
+      <c r="Q73" t="s">
         <v>361</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R73" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="10" t="s">
         <v>647</v>
       </c>
       <c r="B74">
@@ -6449,7 +6563,7 @@
         <v>500</v>
       </c>
       <c r="G74" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E74=F74, E74, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H74" t="s">
@@ -6461,15 +6575,16 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
-      <c r="O74" t="s">
+      <c r="O74" s="4"/>
+      <c r="P74" t="s">
         <v>367</v>
       </c>
-      <c r="P74" t="s">
+      <c r="Q74" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="10" t="s">
         <v>648</v>
       </c>
       <c r="B75">
@@ -6488,7 +6603,7 @@
         <v>500</v>
       </c>
       <c r="G75" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E75=F75, E75, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H75" t="s">
@@ -6503,18 +6618,19 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
-      <c r="O75" t="s">
+      <c r="O75" s="4"/>
+      <c r="P75" t="s">
         <v>370</v>
       </c>
-      <c r="P75" t="s">
+      <c r="Q75" t="s">
         <v>369</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="10" t="s">
         <v>649</v>
       </c>
       <c r="B76">
@@ -6547,17 +6663,18 @@
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
-      <c r="O76" t="s">
+      <c r="O76" s="4"/>
+      <c r="P76" t="s">
         <v>375</v>
       </c>
-      <c r="P76" t="s">
+      <c r="Q76" t="s">
         <v>374</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
         <v>650</v>
       </c>
@@ -6600,15 +6717,15 @@
       <c r="N77" t="s">
         <v>690</v>
       </c>
-      <c r="O77" t="s">
+      <c r="P77" t="s">
         <v>381</v>
       </c>
-      <c r="P77" t="s">
+      <c r="Q77" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="10" t="s">
         <v>651</v>
       </c>
       <c r="B78">
@@ -6641,14 +6758,15 @@
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
-      <c r="O78" t="s">
+      <c r="O78" s="4"/>
+      <c r="P78" t="s">
         <v>386</v>
       </c>
-      <c r="P78" t="s">
+      <c r="Q78" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
         <v>652</v>
       </c>
@@ -6668,7 +6786,7 @@
         <v>498</v>
       </c>
       <c r="G79" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E79=F79, E79, "-")</f>
         <v>Included</v>
       </c>
       <c r="H79" t="s">
@@ -6689,17 +6807,20 @@
       <c r="M79" t="s">
         <v>729</v>
       </c>
-      <c r="N79" t="s">
+      <c r="N79" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O79" t="s">
+      <c r="O79" s="13" t="s">
+        <v>752</v>
+      </c>
+      <c r="P79" t="s">
         <v>390</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
         <v>653</v>
       </c>
@@ -6719,7 +6840,7 @@
         <v>498</v>
       </c>
       <c r="G80" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E80=F80, E80, "-")</f>
         <v>Included</v>
       </c>
       <c r="H80" t="s">
@@ -6740,17 +6861,20 @@
       <c r="M80" t="s">
         <v>688</v>
       </c>
-      <c r="N80" t="s">
+      <c r="N80" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O80" t="s">
+      <c r="O80" s="13" t="s">
+        <v>753</v>
+      </c>
+      <c r="P80" t="s">
         <v>394</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
         <v>654</v>
       </c>
@@ -6770,7 +6894,7 @@
         <v>498</v>
       </c>
       <c r="G81" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(E81=F81, E81, "-")</f>
         <v>Included</v>
       </c>
       <c r="H81" t="s">
@@ -6791,18 +6915,21 @@
       <c r="M81" t="s">
         <v>741</v>
       </c>
-      <c r="N81" t="s">
+      <c r="N81" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="O81" t="s">
+      <c r="O81" s="13" t="s">
+        <v>754</v>
+      </c>
+      <c r="P81" t="s">
         <v>399</v>
       </c>
-      <c r="P81" t="s">
+      <c r="Q81" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="10" t="s">
         <v>655</v>
       </c>
       <c r="B82">
@@ -6835,15 +6962,16 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
-      <c r="O82" t="s">
+      <c r="O82" s="4"/>
+      <c r="P82" t="s">
         <v>404</v>
       </c>
-      <c r="P82" t="s">
+      <c r="Q82" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="10" t="s">
         <v>656</v>
       </c>
       <c r="B83">
@@ -6862,7 +6990,7 @@
         <v>500</v>
       </c>
       <c r="G83" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="G67:G83" si="1">IF(E83=F83, E83, "-")</f>
         <v>Excluded</v>
       </c>
       <c r="H83" t="s">
@@ -6877,15 +7005,16 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
-      <c r="O83" t="s">
+      <c r="O83" s="4"/>
+      <c r="P83" t="s">
         <v>409</v>
       </c>
-      <c r="P83" t="s">
+      <c r="Q83" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="10" t="s">
         <v>657</v>
       </c>
       <c r="B84">
@@ -6918,15 +7047,16 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
-      <c r="O84" t="s">
+      <c r="O84" s="4"/>
+      <c r="P84" t="s">
         <v>414</v>
       </c>
-      <c r="P84" t="s">
+      <c r="Q84" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="10" t="s">
         <v>658</v>
       </c>
       <c r="B85">
@@ -6959,14 +7089,15 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
-      <c r="O85" t="s">
+      <c r="O85" s="4"/>
+      <c r="P85" t="s">
         <v>419</v>
       </c>
-      <c r="P85" t="s">
+      <c r="Q85" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="9" t="s">
         <v>659</v>
       </c>
@@ -7009,15 +7140,15 @@
       <c r="N86" t="s">
         <v>689</v>
       </c>
-      <c r="O86" t="s">
+      <c r="P86" t="s">
         <v>424</v>
       </c>
-      <c r="P86" t="s">
+      <c r="Q86" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="10" t="s">
         <v>660</v>
       </c>
       <c r="B87">
@@ -7051,15 +7182,16 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
-      <c r="O87" t="s">
+      <c r="O87" s="4"/>
+      <c r="P87" t="s">
         <v>429</v>
       </c>
-      <c r="P87" t="s">
+      <c r="Q87" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="10" t="s">
         <v>661</v>
       </c>
       <c r="B88">
@@ -7093,15 +7225,16 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
-      <c r="O88" t="s">
+      <c r="O88" s="4"/>
+      <c r="P88" t="s">
         <v>434</v>
       </c>
-      <c r="P88" t="s">
+      <c r="Q88" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="10" t="s">
         <v>662</v>
       </c>
       <c r="B89">
@@ -7134,15 +7267,16 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
-      <c r="O89" t="s">
+      <c r="O89" s="4"/>
+      <c r="P89" t="s">
         <v>439</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q89" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="10" t="s">
         <v>663</v>
       </c>
       <c r="B90">
@@ -7175,15 +7309,16 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
-      <c r="O90" t="s">
+      <c r="O90" s="4"/>
+      <c r="P90" t="s">
         <v>444</v>
       </c>
-      <c r="P90" t="s">
+      <c r="Q90" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="10" t="s">
         <v>664</v>
       </c>
       <c r="B91">
@@ -7217,15 +7352,16 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
-      <c r="O91" t="s">
+      <c r="O91" s="4"/>
+      <c r="P91" t="s">
         <v>449</v>
       </c>
-      <c r="P91" t="s">
+      <c r="Q91" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="10" t="s">
         <v>665</v>
       </c>
       <c r="B92">
@@ -7258,15 +7394,16 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
-      <c r="O92" t="s">
+      <c r="O92" s="4"/>
+      <c r="P92" t="s">
         <v>454</v>
       </c>
-      <c r="P92" t="s">
+      <c r="Q92" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="10" t="s">
         <v>666</v>
       </c>
       <c r="B93">
@@ -7299,15 +7436,16 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
-      <c r="O93" t="s">
+      <c r="O93" s="4"/>
+      <c r="P93" t="s">
         <v>459</v>
       </c>
-      <c r="P93" t="s">
+      <c r="Q93" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="10" t="s">
         <v>667</v>
       </c>
       <c r="B94">
@@ -7341,14 +7479,15 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
-      <c r="O94" t="s">
+      <c r="O94" s="4"/>
+      <c r="P94" t="s">
         <v>464</v>
       </c>
-      <c r="P94" t="s">
+      <c r="Q94" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="9" t="s">
         <v>668</v>
       </c>
@@ -7391,15 +7530,15 @@
       <c r="N95" t="s">
         <v>690</v>
       </c>
-      <c r="O95" t="s">
+      <c r="P95" t="s">
         <v>469</v>
       </c>
-      <c r="P95" t="s">
+      <c r="Q95" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="10" t="s">
         <v>669</v>
       </c>
       <c r="B96">
@@ -7432,14 +7571,15 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
-      <c r="O96" t="s">
+      <c r="O96" s="4"/>
+      <c r="P96" t="s">
         <v>474</v>
       </c>
-      <c r="P96" t="s">
+      <c r="Q96" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="9" t="s">
         <v>670</v>
       </c>
@@ -7482,15 +7622,15 @@
       <c r="N97" t="s">
         <v>686</v>
       </c>
-      <c r="O97" t="s">
+      <c r="P97" t="s">
         <v>479</v>
       </c>
-      <c r="P97" t="s">
+      <c r="Q97" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="10" t="s">
         <v>671</v>
       </c>
       <c r="B98">
@@ -7523,14 +7663,15 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
-      <c r="O98" t="s">
+      <c r="O98" s="4"/>
+      <c r="P98" t="s">
         <v>484</v>
       </c>
-      <c r="P98" t="s">
+      <c r="Q98" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="9" t="s">
         <v>672</v>
       </c>
@@ -7573,15 +7714,15 @@
       <c r="N99" t="s">
         <v>686</v>
       </c>
-      <c r="O99" t="s">
+      <c r="P99" t="s">
         <v>489</v>
       </c>
-      <c r="P99" t="s">
+      <c r="Q99" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="10" t="s">
         <v>673</v>
       </c>
       <c r="B100">
@@ -7615,20 +7756,144 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
-      <c r="O100" t="s">
+      <c r="O100" s="4"/>
+      <c r="P100" t="s">
         <v>494</v>
       </c>
-      <c r="P100" t="s">
+      <c r="Q100" t="s">
         <v>492</v>
       </c>
     </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="L112" s="11"/>
+      <c r="M112" s="12"/>
+      <c r="N112" s="11"/>
+      <c r="O112" s="11"/>
+    </row>
+    <row r="113" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L113" s="11"/>
+      <c r="M113" s="12"/>
+      <c r="N113" s="11"/>
+      <c r="O113" s="11"/>
+    </row>
+    <row r="114" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L114" s="11"/>
+      <c r="M114" s="12"/>
+      <c r="N114" s="11"/>
+      <c r="O114" s="11"/>
+    </row>
+    <row r="115" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L115" s="11"/>
+      <c r="M115" s="12"/>
+      <c r="N115" s="11"/>
+      <c r="O115" s="11"/>
+    </row>
+    <row r="116" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
+      <c r="N116" s="11"/>
+      <c r="O116" s="11"/>
+    </row>
+    <row r="117" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
+      <c r="N117" s="11"/>
+      <c r="O117" s="11"/>
+    </row>
+    <row r="118" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="11"/>
+      <c r="O118" s="11"/>
+    </row>
+    <row r="119" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
+      <c r="N119" s="11"/>
+      <c r="O119" s="11"/>
+    </row>
+    <row r="120" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
+      <c r="N120" s="11"/>
+      <c r="O120" s="11"/>
+    </row>
+    <row r="121" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
+      <c r="N121" s="11"/>
+      <c r="O121" s="11"/>
+    </row>
+    <row r="122" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="11"/>
+    </row>
+    <row r="123" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L123" s="11"/>
+      <c r="M123" s="11"/>
+      <c r="N123" s="11"/>
+      <c r="O123" s="11"/>
+    </row>
+    <row r="124" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L124" s="11"/>
+      <c r="M124" s="11"/>
+      <c r="N124" s="11"/>
+      <c r="O124" s="11"/>
+    </row>
+    <row r="125" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
+      <c r="N125" s="11"/>
+      <c r="O125" s="11"/>
+    </row>
+    <row r="126" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
+      <c r="N126" s="11"/>
+      <c r="O126" s="11"/>
+    </row>
+    <row r="127" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="11"/>
+      <c r="O127" s="11"/>
+    </row>
+    <row r="128" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
+      <c r="N128" s="11"/>
+      <c r="O128" s="11"/>
+    </row>
+    <row r="129" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
+      <c r="N129" s="11"/>
+      <c r="O129" s="11"/>
+    </row>
+    <row r="130" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L130" s="11"/>
+      <c r="M130" s="12"/>
+      <c r="N130" s="11"/>
+      <c r="O130" s="11"/>
+    </row>
+    <row r="131" spans="12:15" x14ac:dyDescent="0.2">
+      <c r="L131" s="11"/>
+      <c r="M131" s="12"/>
+      <c r="N131" s="11"/>
+      <c r="O131" s="11"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q100" xr:uid="{78A20306-08DA-394C-A3B0-22BFD9DFB649}">
+  <autoFilter ref="A1:R100" xr:uid="{78A20306-08DA-394C-A3B0-22BFD9DFB649}">
     <filterColumn colId="6">
       <filters>
         <filter val="Included"/>
       </filters>
     </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:R81">
+      <sortCondition ref="A1:A100"/>
+    </sortState>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{B3CA492C-FA5E-C54F-99C8-C79C09FD359B}"/>
@@ -7637,13 +7902,13 @@
     <hyperlink ref="K5" r:id="rId4" xr:uid="{CEE0B983-6090-404E-B44A-3C9A94E583DB}"/>
     <hyperlink ref="K6" r:id="rId5" xr:uid="{4A68E3B0-AD56-734E-9849-FC7074610AF2}"/>
     <hyperlink ref="K7" r:id="rId6" xr:uid="{E243574C-E7B0-6C44-A847-DC1D022656DF}"/>
-    <hyperlink ref="K8" r:id="rId7" xr:uid="{EF008BFF-2CBB-DB45-8860-BE8E6675C32B}"/>
+    <hyperlink ref="K69" r:id="rId7" xr:uid="{EF008BFF-2CBB-DB45-8860-BE8E6675C32B}"/>
     <hyperlink ref="K9" r:id="rId8" xr:uid="{6611B9F4-90E2-1242-B6D1-A415287ADB89}"/>
     <hyperlink ref="K10" r:id="rId9" xr:uid="{ACC3F10C-BBAD-364F-8045-1FF313A18A6A}"/>
     <hyperlink ref="K11" r:id="rId10" xr:uid="{8DAA4953-A545-754D-892C-E1F926D7F640}"/>
     <hyperlink ref="K12" r:id="rId11" xr:uid="{BD78689E-624E-5E4C-B9AF-C567F9B6B694}"/>
     <hyperlink ref="K13" r:id="rId12" xr:uid="{E8536DF3-04A5-5649-8FFC-3111C78E71A3}"/>
-    <hyperlink ref="K14" r:id="rId13" xr:uid="{D257C99A-5C39-C340-8037-9850ABAB667D}"/>
+    <hyperlink ref="K8" r:id="rId13" xr:uid="{D257C99A-5C39-C340-8037-9850ABAB667D}"/>
     <hyperlink ref="K15" r:id="rId14" xr:uid="{D4D6B7AF-B843-CE43-AB66-EA61456818B8}"/>
     <hyperlink ref="K16" r:id="rId15" xr:uid="{0BB74315-9639-E24A-A4F3-D9402C457548}"/>
     <hyperlink ref="K17" r:id="rId16" xr:uid="{FC1098D5-8DD0-1747-8E03-32C02CB66CBC}"/>
@@ -7656,7 +7921,7 @@
     <hyperlink ref="K24" r:id="rId23" xr:uid="{2C6D23C6-D30C-4742-BC71-18D52E99C5EA}"/>
     <hyperlink ref="K25" r:id="rId24" xr:uid="{595F8F34-68AC-1F43-9112-7AB329B63187}"/>
     <hyperlink ref="K26" r:id="rId25" xr:uid="{42231814-15A0-B14E-BEEB-686C56C867AC}"/>
-    <hyperlink ref="K27" r:id="rId26" xr:uid="{FB3D3637-E23E-0840-AC7A-FC453C660DDE}"/>
+    <hyperlink ref="K14" r:id="rId26" xr:uid="{FB3D3637-E23E-0840-AC7A-FC453C660DDE}"/>
     <hyperlink ref="K28" r:id="rId27" xr:uid="{C7677016-A6ED-024F-8C63-24F1D7FD286D}"/>
     <hyperlink ref="K29" r:id="rId28" xr:uid="{7E493ACB-EAF4-9346-9CDE-ECABE46DA253}"/>
     <hyperlink ref="K30" r:id="rId29" xr:uid="{641BC2D0-A0DE-0B46-88BD-B59F562F7273}"/>
@@ -7667,26 +7932,26 @@
     <hyperlink ref="K35" r:id="rId34" xr:uid="{29C8AD62-3822-1343-A6AC-B2611DD56EE0}"/>
     <hyperlink ref="K36" r:id="rId35" xr:uid="{8013BE45-8A6F-5F45-992C-82256A3B913A}"/>
     <hyperlink ref="K37" r:id="rId36" xr:uid="{3FDEA1B7-4025-2D40-8DE1-DD2D141916D1}"/>
-    <hyperlink ref="K38" r:id="rId37" xr:uid="{D21A2FD1-B380-BE44-9489-A7F02BA6A4AE}"/>
+    <hyperlink ref="K27" r:id="rId37" xr:uid="{D21A2FD1-B380-BE44-9489-A7F02BA6A4AE}"/>
     <hyperlink ref="K39" r:id="rId38" xr:uid="{0C52E94F-65D4-3147-8B1F-5CEC64C1FB58}"/>
-    <hyperlink ref="K40" r:id="rId39" xr:uid="{61374CE4-FFCB-3046-828B-CB5B1E17C446}"/>
+    <hyperlink ref="K38" r:id="rId39" xr:uid="{61374CE4-FFCB-3046-828B-CB5B1E17C446}"/>
     <hyperlink ref="K41" r:id="rId40" xr:uid="{027CABEF-EB3F-0C4E-9D77-B191657DA714}"/>
     <hyperlink ref="K42" r:id="rId41" xr:uid="{CFDCBDBB-D5EC-7E40-94B6-4928BCAFE3FD}"/>
-    <hyperlink ref="K43" r:id="rId42" xr:uid="{1F35750C-3785-C94D-844D-699A61D16983}"/>
+    <hyperlink ref="K40" r:id="rId42" xr:uid="{1F35750C-3785-C94D-844D-699A61D16983}"/>
     <hyperlink ref="K44" r:id="rId43" xr:uid="{4578AEA1-6DC9-0143-8A1B-60F758690DB6}"/>
     <hyperlink ref="K45" r:id="rId44" xr:uid="{F709BC51-1189-FF4F-808E-49AFB01B65AC}"/>
     <hyperlink ref="K46" r:id="rId45" xr:uid="{6DC85712-9694-CA4F-A06F-2A41565ECF8F}"/>
     <hyperlink ref="K47" r:id="rId46" xr:uid="{2DBB57A2-A469-6A4A-A7B1-E357B096D553}"/>
     <hyperlink ref="K48" r:id="rId47" xr:uid="{13456958-C05D-5E42-830B-F3DF2409AEC1}"/>
     <hyperlink ref="K49" r:id="rId48" xr:uid="{6F59570A-CC03-6246-B5DA-F35554AB8AE4}"/>
-    <hyperlink ref="K50" r:id="rId49" xr:uid="{F5F77297-3D8E-A447-8139-1667739AB66E}"/>
+    <hyperlink ref="K43" r:id="rId49" xr:uid="{F5F77297-3D8E-A447-8139-1667739AB66E}"/>
     <hyperlink ref="K51" r:id="rId50" xr:uid="{9E962F1A-FC47-C242-8099-1D53422E4AFA}"/>
     <hyperlink ref="K52" r:id="rId51" xr:uid="{15304B8E-A005-A149-9D06-5448703F3472}"/>
     <hyperlink ref="K53" r:id="rId52" xr:uid="{090F4804-D95C-7640-9F15-71849573B6EE}"/>
     <hyperlink ref="K54" r:id="rId53" xr:uid="{575F1DBC-E715-9D49-B22C-89D97ED56C74}"/>
-    <hyperlink ref="K55" r:id="rId54" xr:uid="{0850A22F-0E17-EA4E-B649-ECE38AAE6BCF}"/>
+    <hyperlink ref="K50" r:id="rId54" xr:uid="{0850A22F-0E17-EA4E-B649-ECE38AAE6BCF}"/>
     <hyperlink ref="K56" r:id="rId55" xr:uid="{4CF0DF22-1247-1442-B2A5-BFDB6A43645B}"/>
-    <hyperlink ref="K57" r:id="rId56" xr:uid="{282ACFF7-AF5E-9648-879C-92F211D71B45}"/>
+    <hyperlink ref="K55" r:id="rId56" xr:uid="{282ACFF7-AF5E-9648-879C-92F211D71B45}"/>
     <hyperlink ref="K58" r:id="rId57" xr:uid="{AB56B734-A9FD-764C-9F87-0317C499DCD5}"/>
     <hyperlink ref="K59" r:id="rId58" xr:uid="{E9657D46-6229-2649-BA3B-A0C31998B9DE}"/>
     <hyperlink ref="K60" r:id="rId59" xr:uid="{CB01D10A-4D88-654F-A984-BEFD19DDC5BE}"/>
@@ -7698,7 +7963,7 @@
     <hyperlink ref="K66" r:id="rId65" xr:uid="{5D4DD5FF-666C-2740-8678-475B1A72E28B}"/>
     <hyperlink ref="K67" r:id="rId66" xr:uid="{73EE4308-C720-7342-8ACF-F84D3D7F2534}"/>
     <hyperlink ref="K68" r:id="rId67" xr:uid="{167BC61D-E2D9-E14E-9E18-FB2CB474C8DA}"/>
-    <hyperlink ref="K69" r:id="rId68" xr:uid="{274185BF-1551-B049-972F-6B878CFF2E59}"/>
+    <hyperlink ref="K57" r:id="rId68" xr:uid="{274185BF-1551-B049-972F-6B878CFF2E59}"/>
     <hyperlink ref="K70" r:id="rId69" xr:uid="{0D40F30D-307B-794D-80F3-CFBCD5F517A4}"/>
     <hyperlink ref="K71" r:id="rId70" xr:uid="{82C9783D-36EB-4645-8C91-4C1969569FEA}"/>
     <hyperlink ref="K72" r:id="rId71" xr:uid="{E17F6652-7623-B243-B08C-EBFB26C038F0}"/>
